--- a/Helsinki Open Elit 2026/Preliminära Entries - Helsinki Open Elit 2026.xlsx
+++ b/Helsinki Open Elit 2026/Preliminära Entries - Helsinki Open Elit 2026.xlsx
@@ -3,14 +3,16 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="680" yWindow="660" windowWidth="28040" windowHeight="16700" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5265" yWindow="5445" windowWidth="28800" windowHeight="15345" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Preliminära Entries - Helsinki " sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Player Events" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Event Analysis" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Rule Violations" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="timetable" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="timetable" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -39,10 +41,15 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
       <color rgb="00000000"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="62">
     <fill>
       <patternFill/>
     </fill>
@@ -171,8 +178,164 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00fffffa"/>
-        <bgColor rgb="00fffffa"/>
+        <fgColor rgb="FFFFFFFA"/>
+        <bgColor rgb="FFFFFFFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF5DE"/>
+        <bgColor rgb="FFFFF5DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDFFB6"/>
+        <bgColor rgb="FFFDFFB6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD6A5"/>
+        <bgColor rgb="FFFFD6A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6FFDF"/>
+        <bgColor rgb="FFE6FFDF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8FFCF"/>
+        <bgColor rgb="FFD8FFCF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFFDB"/>
+        <bgColor rgb="FFFEFFDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC2C2"/>
+        <bgColor rgb="FFFFC2C2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FFF5"/>
+        <bgColor rgb="FFF9FFF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF5F5"/>
+        <bgColor rgb="FFFFF5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFED"/>
+        <bgColor rgb="FFFFFFED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFDEB3"/>
+        <bgColor rgb="FFFFDEB3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE6C1"/>
+        <bgColor rgb="FFFFE6C1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD6D6"/>
+        <bgColor rgb="FFFFD6D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEED0"/>
+        <bgColor rgb="FFFFEED0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFADAD"/>
+        <bgColor rgb="FFFFADAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAFFBF"/>
+        <bgColor rgb="FFCAFFBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEBEB"/>
+        <bgColor rgb="FFFFEBEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FFEF"/>
+        <bgColor rgb="FFF3FFEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFFC9"/>
+        <bgColor rgb="FFFEFFC9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ffd6a5"/>
+        <bgColor rgb="00ffd6a5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ffdeb3"/>
+        <bgColor rgb="00ffdeb3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00f9fff5"/>
+        <bgColor rgb="00f9fff5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00fdffb6"/>
+        <bgColor rgb="00fdffb6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ffffed"/>
+        <bgColor rgb="00ffffed"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00caffbf"/>
+        <bgColor rgb="00caffbf"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00fff5f5"/>
+        <bgColor rgb="00fff5f5"/>
       </patternFill>
     </fill>
     <fill>
@@ -183,14 +346,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00fdffb6"/>
-        <bgColor rgb="00fdffb6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ffd6a5"/>
-        <bgColor rgb="00ffd6a5"/>
+        <fgColor rgb="00feffdb"/>
+        <bgColor rgb="00feffdb"/>
       </patternFill>
     </fill>
     <fill>
@@ -201,50 +358,44 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00d8ffcf"/>
-        <bgColor rgb="00d8ffcf"/>
+        <fgColor rgb="00fffffa"/>
+        <bgColor rgb="00fffffa"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00feffdb"/>
-        <bgColor rgb="00feffdb"/>
+        <fgColor rgb="00ffadad"/>
+        <bgColor rgb="00ffadad"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ffebeb"/>
+        <bgColor rgb="00ffebeb"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00feffc9"/>
+        <bgColor rgb="00feffc9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ffe6c1"/>
+        <bgColor rgb="00ffe6c1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00f3ffef"/>
+        <bgColor rgb="00f3ffef"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00ffc2c2"/>
         <bgColor rgb="00ffc2c2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00f9fff5"/>
-        <bgColor rgb="00f9fff5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00fff5f5"/>
-        <bgColor rgb="00fff5f5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ffffed"/>
-        <bgColor rgb="00ffffed"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ffdeb3"/>
-        <bgColor rgb="00ffdeb3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ffe6c1"/>
-        <bgColor rgb="00ffe6c1"/>
       </patternFill>
     </fill>
     <fill>
@@ -261,32 +412,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ffadad"/>
-        <bgColor rgb="00ffadad"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00caffbf"/>
-        <bgColor rgb="00caffbf"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ffebeb"/>
-        <bgColor rgb="00ffebeb"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00f3ffef"/>
-        <bgColor rgb="00f3ffef"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00feffc9"/>
-        <bgColor rgb="00feffc9"/>
+        <fgColor rgb="00d8ffcf"/>
+        <bgColor rgb="00d8ffcf"/>
       </patternFill>
     </fill>
   </fills>
@@ -302,7 +429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -411,6 +538,26 @@
     <xf numFmtId="0" fontId="3" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="41" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="40" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="48" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="50" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="52" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="53" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="55" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="56" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="54" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="58" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="59" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="60" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="57" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="61" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -809,7 +956,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D1465"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -15841,7 +15988,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C376"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -20432,7 +20579,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="22" t="inlineStr">
@@ -21768,7 +21915,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -21805,6 +21952,3114 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B3:AY42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="D4" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="E4" s="52" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="F4" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="G4" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="H4" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="I4" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="J4" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="K4" s="45" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="M4" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="N4" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="O4" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="Q4" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="T4" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="V4" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="W4" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="X4" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="Y4" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="Z4" s="60" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="AA4" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AB4" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AC4" s="59" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="AD4" s="59" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="AF4" s="59" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="AG4" s="62" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="AI4" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AK4" s="60" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="AL4" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AM4" s="45" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="AN4" s="57" t="inlineStr">
+        <is>
+          <t>MD V - 1</t>
+        </is>
+      </c>
+      <c r="AO4" s="51" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="AP4" s="55" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="AQ4" s="51" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="AR4" s="51" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="AT4" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AU4" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="AV4" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 3</t>
+        </is>
+      </c>
+      <c r="AW4" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="AX4" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AY4" s="59" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="D5" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="E5" s="52" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="F5" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="G5" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="H5" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="I5" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="J5" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="K5" s="45" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="M5" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="O5" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="Q5" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="T5" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="V5" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="W5" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="X5" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="Y5" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="Z5" s="60" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="AA5" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AC5" s="59" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="AF5" s="59" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="AG5" s="62" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="AI5" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AK5" s="60" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="AL5" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AM5" s="45" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="AN5" s="57" t="inlineStr">
+        <is>
+          <t>MD V - 1</t>
+        </is>
+      </c>
+      <c r="AO5" s="51" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="AP5" s="55" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="AQ5" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 4</t>
+        </is>
+      </c>
+      <c r="AR5" s="51" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="AT5" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AU5" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="AV5" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 3</t>
+        </is>
+      </c>
+      <c r="AW5" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="AX5" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AY5" s="59" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="D6" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="E6" s="52" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="F6" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="G6" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="H6" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="I6" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="J6" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="K6" s="45" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="M6" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="O6" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="Q6" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="T6" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="V6" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="W6" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="X6" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="Y6" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="Z6" s="60" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="AA6" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AC6" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AF6" s="59" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="AG6" s="62" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="AI6" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AK6" s="60" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="AL6" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AN6" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="AO6" s="51" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="AP6" s="55" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="AQ6" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 4</t>
+        </is>
+      </c>
+      <c r="AR6" s="51" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="AT6" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AU6" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="AV6" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 3</t>
+        </is>
+      </c>
+      <c r="AW6" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="AX6" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AY6" s="59" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="E7" s="52" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="F7" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="G7" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="H7" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="I7" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="J7" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K7" s="45" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="M7" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="O7" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="Q7" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="T7" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="V7" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="W7" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="X7" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="Y7" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="Z7" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="AA7" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AC7" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AF7" s="59" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="AG7" s="62" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="AI7" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AK7" s="60" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="AL7" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AN7" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="AP7" s="55" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="AQ7" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 4</t>
+        </is>
+      </c>
+      <c r="AR7" s="51" t="inlineStr">
+        <is>
+          <t>WS V - 1</t>
+        </is>
+      </c>
+      <c r="AT7" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AU7" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="AV7" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 3</t>
+        </is>
+      </c>
+      <c r="AW7" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="AX7" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AY7" s="59" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="E8" s="52" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="G8" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="I8" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K8" s="45" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="M8" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="O8" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="Q8" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="T8" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="V8" s="45" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="W8" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="Y8" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="AA8" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="AC8" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AF8" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AI8" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AL8" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AN8" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="AP8" s="55" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="AQ8" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 4</t>
+        </is>
+      </c>
+      <c r="AR8" s="58" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="AT8" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AU8" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="AV8" s="62" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="AW8" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="AX8" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AY8" s="52" t="inlineStr">
+        <is>
+          <t>XD C - 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="E9" s="52" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="G9" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="I9" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K9" s="45" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="O9" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="Q9" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="T9" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="V9" s="45" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="W9" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="Y9" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="AA9" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="AC9" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AF9" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AI9" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AL9" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AN9" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="AP9" s="55" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="AR9" s="58" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="AT9" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AU9" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="AV9" s="62" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="AW9" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="AX9" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="G10" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="I10" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K10" s="45" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="O10" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="Q10" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="T10" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="V10" s="45" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="W10" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="Y10" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="AA10" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="AC10" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AF10" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AI10" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AL10" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AN10" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="AP10" s="55" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="AR10" s="58" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="AT10" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AU10" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="AV10" s="62" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="AW10" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="AX10" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 1</t>
+        </is>
+      </c>
+      <c r="G11" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="I11" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K11" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="O11" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="Q11" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="T11" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="V11" s="45" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="W11" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="Y11" s="55" t="inlineStr">
+        <is>
+          <t>WD B - 1</t>
+        </is>
+      </c>
+      <c r="AA11" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="AC11" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AF11" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AI11" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AL11" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AN11" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="AP11" s="55" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="AR11" s="58" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="AT11" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AU11" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="AV11" s="62" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="AW11" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="AX11" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="I12" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K12" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="Q12" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="T12" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="Y12" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AA12" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="AC12" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AF12" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AI12" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AN12" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="AR12" s="58" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="I13" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K13" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="Q13" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="T13" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="Y13" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AA13" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="AC13" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AF13" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AI13" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AN13" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="AR13" s="58" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="I14" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K14" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="Q14" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 1</t>
+        </is>
+      </c>
+      <c r="T14" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="Y14" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AA14" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="AC14" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AF14" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AI14" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AN14" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="AR14" s="63" t="inlineStr">
+        <is>
+          <t>WD C - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="I15" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="K15" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="Q15" s="52" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="T15" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="Y15" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AA15" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="AC15" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AF15" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
+        </is>
+      </c>
+      <c r="AI15" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AN15" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q16" s="52" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="T16" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AC16" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="AI16" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AN16" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q17" s="52" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="T17" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AC17" s="52" t="inlineStr">
+        <is>
+          <t>XD C - 3</t>
+        </is>
+      </c>
+      <c r="AI17" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q18" s="52" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="T18" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AC18" s="52" t="inlineStr">
+        <is>
+          <t>XD C - 3</t>
+        </is>
+      </c>
+      <c r="AI18" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>16</v>
+      </c>
+      <c r="T19" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AI19" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20">
+        <f>COUNTA(C4:D19)</f>
+        <v/>
+      </c>
+      <c r="D20">
+        <f>COUNTA(D4:E19)</f>
+        <v/>
+      </c>
+      <c r="E20">
+        <f>COUNTA(E4:F19)</f>
+        <v/>
+      </c>
+      <c r="F20">
+        <f>COUNTA(F4:G19)</f>
+        <v/>
+      </c>
+      <c r="G20">
+        <f>COUNTA(G4:H19)</f>
+        <v/>
+      </c>
+      <c r="H20">
+        <f>COUNTA(H4:I19)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>COUNTA(I4:J19)</f>
+        <v/>
+      </c>
+      <c r="J20">
+        <f>COUNTA(J4:K19)</f>
+        <v/>
+      </c>
+      <c r="K20">
+        <f>COUNTA(K4:L19)</f>
+        <v/>
+      </c>
+      <c r="L20">
+        <f>COUNTA(L4:M19)</f>
+        <v/>
+      </c>
+      <c r="M20">
+        <f>COUNTA(M4:N19)</f>
+        <v/>
+      </c>
+      <c r="N20">
+        <f>COUNTA(N4:O19)</f>
+        <v/>
+      </c>
+      <c r="O20">
+        <f>COUNTA(O4:P19)</f>
+        <v/>
+      </c>
+      <c r="P20">
+        <f>COUNTA(P4:Q19)</f>
+        <v/>
+      </c>
+      <c r="Q20">
+        <f>COUNTA(Q4:R19)</f>
+        <v/>
+      </c>
+      <c r="R20">
+        <f>COUNTA(R4:S19)</f>
+        <v/>
+      </c>
+      <c r="S20">
+        <f>COUNTA(S4:T19)</f>
+        <v/>
+      </c>
+      <c r="T20">
+        <f>COUNTA(T4:U19)</f>
+        <v/>
+      </c>
+      <c r="U20">
+        <f>COUNTA(U4:V19)</f>
+        <v/>
+      </c>
+      <c r="V20">
+        <f>COUNTA(V4:W19)</f>
+        <v/>
+      </c>
+      <c r="W20">
+        <f>COUNTA(W4:X19)</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>COUNTA(X4:Y19)</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>COUNTA(Y4:Z19)</f>
+        <v/>
+      </c>
+      <c r="Z20">
+        <f>COUNTA(Z4:AA19)</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>COUNTA(AA4:AB19)</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>COUNTA(AB4:AC19)</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>COUNTA(AC4:AD19)</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>COUNTA(AD4:AE19)</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>COUNTA(AE4:AF19)</f>
+        <v/>
+      </c>
+      <c r="AF20">
+        <f>COUNTA(AF4:AG19)</f>
+        <v/>
+      </c>
+      <c r="AG20">
+        <f>COUNTA(AG4:AH19)</f>
+        <v/>
+      </c>
+      <c r="AH20">
+        <f>COUNTA(AH4:AI19)</f>
+        <v/>
+      </c>
+      <c r="AI20">
+        <f>COUNTA(AI4:AJ19)</f>
+        <v/>
+      </c>
+      <c r="AJ20">
+        <f>COUNTA(AJ4:AK19)</f>
+        <v/>
+      </c>
+      <c r="AK20">
+        <f>COUNTA(AK4:AL19)</f>
+        <v/>
+      </c>
+      <c r="AL20">
+        <f>COUNTA(AL4:AM19)</f>
+        <v/>
+      </c>
+      <c r="AM20">
+        <f>COUNTA(AM4:AN19)</f>
+        <v/>
+      </c>
+      <c r="AN20">
+        <f>COUNTA(AN4:AO19)</f>
+        <v/>
+      </c>
+      <c r="AO20">
+        <f>COUNTA(AO4:AP19)</f>
+        <v/>
+      </c>
+      <c r="AP20">
+        <f>COUNTA(AP4:AQ19)</f>
+        <v/>
+      </c>
+      <c r="AQ20">
+        <f>COUNTA(AQ4:AR19)</f>
+        <v/>
+      </c>
+      <c r="AR20">
+        <f>COUNTA(AR4:AS19)</f>
+        <v/>
+      </c>
+      <c r="AS20">
+        <f>COUNTA(AS4:AT19)</f>
+        <v/>
+      </c>
+      <c r="AT20">
+        <f>COUNTA(AT4:AU19)</f>
+        <v/>
+      </c>
+      <c r="AU20">
+        <f>COUNTA(AU4:AV19)</f>
+        <v/>
+      </c>
+      <c r="AV20">
+        <f>COUNTA(AV4:AW19)</f>
+        <v/>
+      </c>
+      <c r="AW20">
+        <f>COUNTA(AW4:AX19)</f>
+        <v/>
+      </c>
+      <c r="AX20">
+        <f>COUNTA(AX4:AY19)</f>
+        <v/>
+      </c>
+      <c r="AY20">
+        <f>COUNTA(AY4:AZ19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="F26" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="G26" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="H26" s="58" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="I26" s="51" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="J26" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 5</t>
+        </is>
+      </c>
+      <c r="L26" s="57" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="M26" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 4</t>
+        </is>
+      </c>
+      <c r="O26" s="49" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="P26" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 4</t>
+        </is>
+      </c>
+      <c r="Q26" s="45" t="inlineStr">
+        <is>
+          <t>XD A - 4</t>
+        </is>
+      </c>
+      <c r="S26" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="T26" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="U26" s="59" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="V26" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="W26" s="49" t="inlineStr">
+        <is>
+          <t>WS C - 3</t>
+        </is>
+      </c>
+      <c r="Y26" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 5</t>
+        </is>
+      </c>
+      <c r="AB26" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 5</t>
+        </is>
+      </c>
+      <c r="AC26" s="60" t="inlineStr">
+        <is>
+          <t>WD V - 3</t>
+        </is>
+      </c>
+      <c r="AD26" s="55" t="inlineStr">
+        <is>
+          <t>WD B - 4</t>
+        </is>
+      </c>
+      <c r="AE26" s="57" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="AF26" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 5</t>
+        </is>
+      </c>
+      <c r="AH26" s="62" t="inlineStr">
+        <is>
+          <t>WS B - 4</t>
+        </is>
+      </c>
+      <c r="AI26" s="59" t="inlineStr">
+        <is>
+          <t>MS V - 4</t>
+        </is>
+      </c>
+      <c r="AJ26" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 6</t>
+        </is>
+      </c>
+      <c r="AL26" s="55" t="inlineStr">
+        <is>
+          <t>WD B - 5</t>
+        </is>
+      </c>
+      <c r="AM26" s="51" t="inlineStr">
+        <is>
+          <t>WS V - 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="F27" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="G27" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="H27" s="58" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="I27" s="51" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="J27" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 5</t>
+        </is>
+      </c>
+      <c r="L27" s="57" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="M27" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 4</t>
+        </is>
+      </c>
+      <c r="O27" s="49" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="P27" s="53" t="inlineStr">
+        <is>
+          <t>XD V - 4</t>
+        </is>
+      </c>
+      <c r="S27" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="T27" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="U27" s="59" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="V27" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="W27" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 4</t>
+        </is>
+      </c>
+      <c r="Y27" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 5</t>
+        </is>
+      </c>
+      <c r="AB27" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 5</t>
+        </is>
+      </c>
+      <c r="AC27" s="60" t="inlineStr">
+        <is>
+          <t>WD V - 3</t>
+        </is>
+      </c>
+      <c r="AD27" s="55" t="inlineStr">
+        <is>
+          <t>WD B - 4</t>
+        </is>
+      </c>
+      <c r="AE27" s="57" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="AF27" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 5</t>
+        </is>
+      </c>
+      <c r="AI27" s="60" t="inlineStr">
+        <is>
+          <t>WD V - 4</t>
+        </is>
+      </c>
+      <c r="AJ27" s="58" t="inlineStr">
+        <is>
+          <t>WD A - 4</t>
+        </is>
+      </c>
+      <c r="AM27" s="57" t="inlineStr">
+        <is>
+          <t>MD V - 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="F28" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="G28" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="H28" s="58" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="I28" s="51" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="J28" s="55" t="inlineStr">
+        <is>
+          <t>WD B - 3</t>
+        </is>
+      </c>
+      <c r="L28" s="57" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="M28" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 4</t>
+        </is>
+      </c>
+      <c r="P28" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 4</t>
+        </is>
+      </c>
+      <c r="S28" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="T28" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="U28" s="51" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="V28" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="W28" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 4</t>
+        </is>
+      </c>
+      <c r="AB28" s="58" t="inlineStr">
+        <is>
+          <t>WD A - 3</t>
+        </is>
+      </c>
+      <c r="AC28" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 5</t>
+        </is>
+      </c>
+      <c r="AI28" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 6</t>
+        </is>
+      </c>
+      <c r="AJ28" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 6</t>
+        </is>
+      </c>
+      <c r="AM28" s="50" t="inlineStr">
+        <is>
+          <t>MD B - 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="F29" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="G29" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="H29" s="58" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="I29" s="51" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="J29" s="55" t="inlineStr">
+        <is>
+          <t>WD B - 3</t>
+        </is>
+      </c>
+      <c r="L29" s="57" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="M29" s="56" t="inlineStr">
+        <is>
+          <t>MD A - 4</t>
+        </is>
+      </c>
+      <c r="P29" s="44" t="inlineStr">
+        <is>
+          <t>XD B - 4</t>
+        </is>
+      </c>
+      <c r="S29" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
+        </is>
+      </c>
+      <c r="T29" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="U29" s="51" t="inlineStr">
+        <is>
+          <t>WS V - 3</t>
+        </is>
+      </c>
+      <c r="V29" s="47" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="AB29" s="58" t="inlineStr">
+        <is>
+          <t>WD A - 3</t>
+        </is>
+      </c>
+      <c r="AC29" s="46" t="inlineStr">
+        <is>
+          <t>MS B - 5</t>
+        </is>
+      </c>
+      <c r="AJ29" s="63" t="inlineStr">
+        <is>
+          <t>WD C - 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="H30" s="49" t="inlineStr">
+        <is>
+          <t>WS C - 1</t>
+        </is>
+      </c>
+      <c r="J30" s="55" t="inlineStr">
+        <is>
+          <t>WD B - 3</t>
+        </is>
+      </c>
+      <c r="M30" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="S30" s="63" t="inlineStr">
+        <is>
+          <t>WD C - 2</t>
+        </is>
+      </c>
+      <c r="U30" s="54" t="inlineStr">
+        <is>
+          <t>WS A - 5</t>
+        </is>
+      </c>
+      <c r="AB30" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="H31" s="49" t="inlineStr">
+        <is>
+          <t>WS C - 1</t>
+        </is>
+      </c>
+      <c r="J31" s="55" t="inlineStr">
+        <is>
+          <t>WD B - 3</t>
+        </is>
+      </c>
+      <c r="M31" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="S31" s="63" t="inlineStr">
+        <is>
+          <t>WD C - 2</t>
+        </is>
+      </c>
+      <c r="U31" s="62" t="inlineStr">
+        <is>
+          <t>WS B - 3</t>
+        </is>
+      </c>
+      <c r="AB31" s="61" t="inlineStr">
+        <is>
+          <t>MS C - 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>7</v>
+      </c>
+      <c r="F32" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="H32" s="49" t="inlineStr">
+        <is>
+          <t>WS C - 1</t>
+        </is>
+      </c>
+      <c r="M32" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="S32" s="63" t="inlineStr">
+        <is>
+          <t>WD C - 2</t>
+        </is>
+      </c>
+      <c r="U32" s="62" t="inlineStr">
+        <is>
+          <t>WS B - 3</t>
+        </is>
+      </c>
+      <c r="AB32" s="63" t="inlineStr">
+        <is>
+          <t>WD C - 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="H33" s="49" t="inlineStr">
+        <is>
+          <t>WS C - 1</t>
+        </is>
+      </c>
+      <c r="M33" s="48" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="S33" s="63" t="inlineStr">
+        <is>
+          <t>WD C - 2</t>
+        </is>
+      </c>
+      <c r="AB33" s="63" t="inlineStr">
+        <is>
+          <t>WD C - 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42">
+        <f>COUNTA(C26:D41)</f>
+        <v/>
+      </c>
+      <c r="D42">
+        <f>COUNTA(D26:E41)</f>
+        <v/>
+      </c>
+      <c r="E42">
+        <f>COUNTA(E26:F41)</f>
+        <v/>
+      </c>
+      <c r="F42">
+        <f>COUNTA(F26:G41)</f>
+        <v/>
+      </c>
+      <c r="G42">
+        <f>COUNTA(G26:H41)</f>
+        <v/>
+      </c>
+      <c r="H42">
+        <f>COUNTA(H26:I41)</f>
+        <v/>
+      </c>
+      <c r="I42">
+        <f>COUNTA(I26:J41)</f>
+        <v/>
+      </c>
+      <c r="J42">
+        <f>COUNTA(J26:K41)</f>
+        <v/>
+      </c>
+      <c r="K42">
+        <f>COUNTA(K26:L41)</f>
+        <v/>
+      </c>
+      <c r="L42">
+        <f>COUNTA(L26:M41)</f>
+        <v/>
+      </c>
+      <c r="M42">
+        <f>COUNTA(M26:N41)</f>
+        <v/>
+      </c>
+      <c r="N42">
+        <f>COUNTA(N26:O41)</f>
+        <v/>
+      </c>
+      <c r="O42">
+        <f>COUNTA(O26:P41)</f>
+        <v/>
+      </c>
+      <c r="P42">
+        <f>COUNTA(P26:Q41)</f>
+        <v/>
+      </c>
+      <c r="Q42">
+        <f>COUNTA(Q26:R41)</f>
+        <v/>
+      </c>
+      <c r="R42">
+        <f>COUNTA(R26:S41)</f>
+        <v/>
+      </c>
+      <c r="S42">
+        <f>COUNTA(S26:T41)</f>
+        <v/>
+      </c>
+      <c r="T42">
+        <f>COUNTA(T26:U41)</f>
+        <v/>
+      </c>
+      <c r="U42">
+        <f>COUNTA(U26:V41)</f>
+        <v/>
+      </c>
+      <c r="V42">
+        <f>COUNTA(V26:W41)</f>
+        <v/>
+      </c>
+      <c r="W42">
+        <f>COUNTA(W26:X41)</f>
+        <v/>
+      </c>
+      <c r="X42">
+        <f>COUNTA(X26:Y41)</f>
+        <v/>
+      </c>
+      <c r="Y42">
+        <f>COUNTA(Y26:Z41)</f>
+        <v/>
+      </c>
+      <c r="Z42">
+        <f>COUNTA(Z26:AA41)</f>
+        <v/>
+      </c>
+      <c r="AA42">
+        <f>COUNTA(AA26:AB41)</f>
+        <v/>
+      </c>
+      <c r="AB42">
+        <f>COUNTA(AB26:AC41)</f>
+        <v/>
+      </c>
+      <c r="AC42">
+        <f>COUNTA(AC26:AD41)</f>
+        <v/>
+      </c>
+      <c r="AD42">
+        <f>COUNTA(AD26:AE41)</f>
+        <v/>
+      </c>
+      <c r="AE42">
+        <f>COUNTA(AE26:AF41)</f>
+        <v/>
+      </c>
+      <c r="AF42">
+        <f>COUNTA(AF26:AG41)</f>
+        <v/>
+      </c>
+      <c r="AG42">
+        <f>COUNTA(AG26:AH41)</f>
+        <v/>
+      </c>
+      <c r="AH42">
+        <f>COUNTA(AH26:AI41)</f>
+        <v/>
+      </c>
+      <c r="AI42">
+        <f>COUNTA(AI26:AJ41)</f>
+        <v/>
+      </c>
+      <c r="AJ42">
+        <f>COUNTA(AJ26:AK41)</f>
+        <v/>
+      </c>
+      <c r="AK42">
+        <f>COUNTA(AK26:AL41)</f>
+        <v/>
+      </c>
+      <c r="AL42">
+        <f>COUNTA(AL26:AM41)</f>
+        <v/>
+      </c>
+      <c r="AM42">
+        <f>COUNTA(AM26:AN41)</f>
+        <v/>
+      </c>
+      <c r="AN42">
+        <f>COUNTA(AN26:AO41)</f>
+        <v/>
+      </c>
+      <c r="AO42">
+        <f>COUNTA(AO26:AP41)</f>
+        <v/>
+      </c>
+      <c r="AP42">
+        <f>COUNTA(AP26:AQ41)</f>
+        <v/>
+      </c>
+      <c r="AQ42">
+        <f>COUNTA(AQ26:AR41)</f>
+        <v/>
+      </c>
+      <c r="AR42">
+        <f>COUNTA(AR26:AS41)</f>
+        <v/>
+      </c>
+      <c r="AS42">
+        <f>COUNTA(AS26:AT41)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B3:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -22059,159 +25314,174 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="44" t="inlineStr">
+      <c r="D4" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="F4" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="H4" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="J4" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="L4" s="67" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="M4" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 1</t>
+        </is>
+      </c>
+      <c r="N4" s="69" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="P4" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="R4" s="70" t="inlineStr">
         <is>
           <t>XD B - 1</t>
         </is>
       </c>
-      <c r="M4" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 1</t>
-        </is>
-      </c>
-      <c r="N4" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="P4" s="56" t="inlineStr">
+      <c r="S4" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="T4" s="71" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="V4" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="X4" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="Y4" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="Z4" s="72" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="AB4" s="70" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AC4" s="72" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="AD4" s="71" t="inlineStr">
+        <is>
+          <t>XD C - 3</t>
+        </is>
+      </c>
+      <c r="AE4" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AF4" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="AG4" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AH4" s="74" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="AI4" s="75" t="inlineStr">
         <is>
           <t>MD A - 1</t>
         </is>
       </c>
-      <c r="Q4" s="51" t="inlineStr">
+      <c r="AJ4" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AK4" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AL4" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="AM4" s="77" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="AO4" s="75" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AP4" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 3</t>
+        </is>
+      </c>
+      <c r="AR4" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AT4" s="78" t="inlineStr">
         <is>
           <t>WS V - 1</t>
         </is>
       </c>
-      <c r="R4" s="52" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="T4" s="51" t="inlineStr">
+      <c r="AU4" s="75" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="AW4" s="78" t="inlineStr">
         <is>
           <t>WS V - 1</t>
         </is>
       </c>
-      <c r="V4" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="W4" s="56" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="X4" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="Z4" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="AB4" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AC4" s="45" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="AD4" s="44" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="AE4" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AF4" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="AG4" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AI4" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="AK4" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AL4" s="45" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="AM4" s="44" t="inlineStr">
-        <is>
-          <t>XD B - 4</t>
-        </is>
-      </c>
-      <c r="AO4" s="57" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AP4" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 3</t>
-        </is>
-      </c>
-      <c r="AQ4" s="52" t="inlineStr">
-        <is>
-          <t>XD C - 4</t>
-        </is>
-      </c>
-      <c r="AR4" s="51" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AS4" s="44" t="inlineStr">
-        <is>
-          <t>XD B - 5</t>
-        </is>
-      </c>
-      <c r="AU4" s="59" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="AV4" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AW4" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AX4" s="59" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="AY4" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 4</t>
+      <c r="AX4" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
         </is>
       </c>
     </row>
@@ -22219,149 +25489,169 @@
       <c r="B5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" s="44" t="inlineStr">
+      <c r="D5" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="F5" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="H5" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="J5" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="L5" s="67" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="N5" s="69" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="P5" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="R5" s="70" t="inlineStr">
         <is>
           <t>XD B - 1</t>
         </is>
       </c>
-      <c r="M5" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 1</t>
-        </is>
-      </c>
-      <c r="N5" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="P5" s="56" t="inlineStr">
+      <c r="S5" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="T5" s="71" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="V5" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="X5" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="Y5" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="Z5" s="72" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="AB5" s="70" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AC5" s="72" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="AD5" s="71" t="inlineStr">
+        <is>
+          <t>XD C - 3</t>
+        </is>
+      </c>
+      <c r="AE5" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AF5" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="AG5" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AH5" s="74" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="AI5" s="75" t="inlineStr">
         <is>
           <t>MD A - 1</t>
         </is>
       </c>
-      <c r="Q5" s="51" t="inlineStr">
+      <c r="AJ5" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AK5" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AL5" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="AM5" s="77" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="AO5" s="75" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AP5" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 3</t>
+        </is>
+      </c>
+      <c r="AR5" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AT5" s="78" t="inlineStr">
         <is>
           <t>WS V - 1</t>
         </is>
       </c>
-      <c r="R5" s="52" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="T5" s="51" t="inlineStr">
+      <c r="AU5" s="75" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="AW5" s="78" t="inlineStr">
         <is>
           <t>WS V - 1</t>
         </is>
       </c>
-      <c r="V5" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="W5" s="56" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="X5" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="Z5" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="AB5" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AC5" s="45" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="AD5" s="44" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="AE5" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AF5" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="AG5" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AI5" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="AK5" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AL5" s="45" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="AM5" s="44" t="inlineStr">
-        <is>
-          <t>XD B - 4</t>
-        </is>
-      </c>
-      <c r="AO5" s="57" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AP5" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 3</t>
-        </is>
-      </c>
-      <c r="AR5" s="51" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AU5" s="59" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="AV5" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AW5" s="62" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AX5" s="59" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
-        </is>
-      </c>
-      <c r="AY5" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 4</t>
+      <c r="AX5" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
         </is>
       </c>
     </row>
@@ -22369,139 +25659,159 @@
       <c r="B6" t="n">
         <v>3</v>
       </c>
-      <c r="L6" s="44" t="inlineStr">
+      <c r="D6" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="F6" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="H6" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="J6" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 1</t>
+        </is>
+      </c>
+      <c r="L6" s="67" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="N6" s="69" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="P6" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="R6" s="70" t="inlineStr">
         <is>
           <t>XD B - 1</t>
         </is>
       </c>
-      <c r="M6" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 1</t>
-        </is>
-      </c>
-      <c r="N6" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="P6" s="56" t="inlineStr">
+      <c r="S6" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="T6" s="71" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="V6" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="X6" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="Z6" s="72" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="AB6" s="70" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AC6" s="77" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="AE6" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AF6" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="AG6" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AH6" s="74" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="AI6" s="75" t="inlineStr">
         <is>
           <t>MD A - 1</t>
         </is>
       </c>
-      <c r="Q6" s="51" t="inlineStr">
+      <c r="AJ6" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AK6" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AL6" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="AM6" s="77" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="AO6" s="75" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AP6" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 3</t>
+        </is>
+      </c>
+      <c r="AR6" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AT6" s="78" t="inlineStr">
         <is>
           <t>WS V - 1</t>
         </is>
       </c>
-      <c r="R6" s="52" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="T6" s="51" t="inlineStr">
+      <c r="AU6" s="75" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="AW6" s="78" t="inlineStr">
         <is>
           <t>WS V - 1</t>
         </is>
       </c>
-      <c r="V6" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="W6" s="56" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="X6" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="Z6" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="AB6" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AC6" s="45" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="AD6" s="44" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="AE6" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AF6" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="AG6" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AI6" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="AK6" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AL6" s="45" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="AO6" s="57" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AP6" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 3</t>
-        </is>
-      </c>
-      <c r="AR6" s="51" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AU6" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 4</t>
-        </is>
-      </c>
-      <c r="AV6" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AW6" s="62" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AX6" s="59" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
+      <c r="AX6" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
         </is>
       </c>
     </row>
@@ -22509,129 +25819,159 @@
       <c r="B7" t="n">
         <v>4</v>
       </c>
-      <c r="L7" s="44" t="inlineStr">
+      <c r="D7" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="F7" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="H7" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="J7" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="L7" s="67" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="N7" s="69" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="P7" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="R7" s="70" t="inlineStr">
         <is>
           <t>XD B - 1</t>
         </is>
       </c>
-      <c r="N7" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="P7" s="56" t="inlineStr">
+      <c r="S7" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 2</t>
+        </is>
+      </c>
+      <c r="T7" s="71" t="inlineStr">
+        <is>
+          <t>XD C - 2</t>
+        </is>
+      </c>
+      <c r="V7" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="X7" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="Z7" s="72" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="AB7" s="70" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AC7" s="77" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="AE7" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AF7" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="AG7" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AH7" s="74" t="inlineStr">
+        <is>
+          <t>WS B - 1</t>
+        </is>
+      </c>
+      <c r="AI7" s="75" t="inlineStr">
         <is>
           <t>MD A - 1</t>
         </is>
       </c>
-      <c r="Q7" s="51" t="inlineStr">
+      <c r="AJ7" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AK7" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AL7" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 4</t>
+        </is>
+      </c>
+      <c r="AM7" s="77" t="inlineStr">
+        <is>
+          <t>WD V - 2</t>
+        </is>
+      </c>
+      <c r="AO7" s="75" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AP7" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 3</t>
+        </is>
+      </c>
+      <c r="AR7" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AT7" s="79" t="inlineStr">
+        <is>
+          <t>MD V - 1</t>
+        </is>
+      </c>
+      <c r="AU7" s="75" t="inlineStr">
+        <is>
+          <t>MD A - 3</t>
+        </is>
+      </c>
+      <c r="AW7" s="78" t="inlineStr">
         <is>
           <t>WS V - 1</t>
         </is>
       </c>
-      <c r="R7" s="52" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="T7" s="57" t="inlineStr">
-        <is>
-          <t>MD V - 1</t>
-        </is>
-      </c>
-      <c r="V7" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="W7" s="56" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="X7" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 1</t>
-        </is>
-      </c>
-      <c r="Z7" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="AB7" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AC7" s="45" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="AD7" s="44" t="inlineStr">
-        <is>
-          <t>XD B - 3</t>
-        </is>
-      </c>
-      <c r="AF7" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 3</t>
-        </is>
-      </c>
-      <c r="AG7" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AI7" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="AK7" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 3</t>
-        </is>
-      </c>
-      <c r="AL7" s="45" t="inlineStr">
-        <is>
-          <t>XD A - 2</t>
-        </is>
-      </c>
-      <c r="AO7" s="57" t="inlineStr">
-        <is>
-          <t>MD V - 2</t>
-        </is>
-      </c>
-      <c r="AP7" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 3</t>
-        </is>
-      </c>
-      <c r="AR7" s="51" t="inlineStr">
-        <is>
-          <t>WS V - 2</t>
-        </is>
-      </c>
-      <c r="AU7" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 4</t>
-        </is>
-      </c>
-      <c r="AV7" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AW7" s="62" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AX7" s="59" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
+      <c r="AX7" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
         </is>
       </c>
     </row>
@@ -22639,94 +25979,134 @@
       <c r="B8" t="n">
         <v>5</v>
       </c>
-      <c r="L8" s="44" t="inlineStr">
+      <c r="D8" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="F8" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="H8" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="J8" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="L8" s="67" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="N8" s="69" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="P8" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="R8" s="70" t="inlineStr">
         <is>
           <t>XD B - 1</t>
         </is>
       </c>
-      <c r="N8" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="P8" s="56" t="inlineStr">
+      <c r="S8" s="67" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="V8" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="X8" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="Z8" s="72" t="inlineStr">
+        <is>
+          <t>MS V - 1</t>
+        </is>
+      </c>
+      <c r="AB8" s="70" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AC8" s="77" t="inlineStr">
+        <is>
+          <t>WD V - 1</t>
+        </is>
+      </c>
+      <c r="AE8" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AF8" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="AG8" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AI8" s="75" t="inlineStr">
         <is>
           <t>MD A - 1</t>
         </is>
       </c>
-      <c r="Q8" s="51" t="inlineStr">
+      <c r="AK8" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AM8" s="69" t="inlineStr">
+        <is>
+          <t>WD B - 3</t>
+        </is>
+      </c>
+      <c r="AO8" s="75" t="inlineStr">
+        <is>
+          <t>MD A - 2</t>
+        </is>
+      </c>
+      <c r="AR8" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AT8" s="79" t="inlineStr">
+        <is>
+          <t>MD V - 1</t>
+        </is>
+      </c>
+      <c r="AU8" s="71" t="inlineStr">
+        <is>
+          <t>XD C - 4</t>
+        </is>
+      </c>
+      <c r="AW8" s="78" t="inlineStr">
         <is>
           <t>WS V - 1</t>
         </is>
       </c>
-      <c r="R8" s="52" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="T8" s="57" t="inlineStr">
-        <is>
-          <t>MD V - 1</t>
-        </is>
-      </c>
-      <c r="V8" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="W8" s="56" t="inlineStr">
-        <is>
-          <t>MD A - 2</t>
-        </is>
-      </c>
-      <c r="Z8" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="AB8" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 2</t>
-        </is>
-      </c>
-      <c r="AC8" s="45" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="AG8" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AI8" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="AK8" s="52" t="inlineStr">
-        <is>
-          <t>XD C - 3</t>
-        </is>
-      </c>
-      <c r="AP8" s="56" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="AV8" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AW8" s="62" t="inlineStr">
-        <is>
-          <t>WS B - 1</t>
-        </is>
-      </c>
-      <c r="AX8" s="59" t="inlineStr">
-        <is>
-          <t>MS V - 1</t>
+      <c r="AX8" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
         </is>
       </c>
     </row>
@@ -22734,84 +26114,119 @@
       <c r="B9" t="n">
         <v>6</v>
       </c>
-      <c r="L9" s="44" t="inlineStr">
+      <c r="D9" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="F9" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="H9" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="J9" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="L9" s="67" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="N9" s="69" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="P9" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="R9" s="70" t="inlineStr">
         <is>
           <t>XD B - 1</t>
         </is>
       </c>
-      <c r="N9" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="P9" s="56" t="inlineStr">
+      <c r="S9" s="67" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="V9" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="X9" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="Z9" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="AB9" s="70" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AE9" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AF9" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="AG9" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AI9" s="75" t="inlineStr">
         <is>
           <t>MD A - 1</t>
         </is>
       </c>
-      <c r="R9" s="52" t="inlineStr">
-        <is>
-          <t>XD C - 1</t>
-        </is>
-      </c>
-      <c r="T9" s="44" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="V9" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="W9" s="56" t="inlineStr">
+      <c r="AK9" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AM9" s="69" t="inlineStr">
+        <is>
+          <t>WD B - 3</t>
+        </is>
+      </c>
+      <c r="AO9" s="75" t="inlineStr">
         <is>
           <t>MD A - 2</t>
         </is>
       </c>
-      <c r="Z9" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="AB9" s="52" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="AC9" s="45" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="AG9" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AI9" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="AK9" s="52" t="inlineStr">
-        <is>
-          <t>XD C - 3</t>
-        </is>
-      </c>
-      <c r="AP9" s="56" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="AV9" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AX9" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
+      <c r="AR9" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AT9" s="81" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="AX9" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
         </is>
       </c>
     </row>
@@ -22819,74 +26234,119 @@
       <c r="B10" t="n">
         <v>7</v>
       </c>
-      <c r="L10" s="44" t="inlineStr">
+      <c r="D10" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="F10" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="H10" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="J10" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="L10" s="67" t="inlineStr">
+        <is>
+          <t>XD A - 1</t>
+        </is>
+      </c>
+      <c r="N10" s="69" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="P10" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="R10" s="70" t="inlineStr">
         <is>
           <t>XD B - 1</t>
         </is>
       </c>
-      <c r="N10" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="P10" s="56" t="inlineStr">
+      <c r="S10" s="67" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="V10" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="X10" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="Z10" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="AB10" s="70" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AE10" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AF10" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="AG10" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AI10" s="75" t="inlineStr">
         <is>
           <t>MD A - 1</t>
         </is>
       </c>
-      <c r="T10" s="44" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="V10" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="W10" s="56" t="inlineStr">
+      <c r="AK10" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AM10" s="69" t="inlineStr">
+        <is>
+          <t>WD B - 3</t>
+        </is>
+      </c>
+      <c r="AO10" s="75" t="inlineStr">
         <is>
           <t>MD A - 2</t>
         </is>
       </c>
-      <c r="Z10" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="AB10" s="52" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="AC10" s="45" t="inlineStr">
-        <is>
-          <t>XD A - 1</t>
-        </is>
-      </c>
-      <c r="AG10" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AI10" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="AP10" s="56" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="AV10" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AX10" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
+      <c r="AR10" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AT10" s="81" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="AX10" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
         </is>
       </c>
     </row>
@@ -22894,69 +26354,114 @@
       <c r="B11" t="n">
         <v>8</v>
       </c>
-      <c r="L11" s="44" t="inlineStr">
+      <c r="D11" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="F11" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="H11" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="J11" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="N11" s="69" t="inlineStr">
+        <is>
+          <t>WD B - 2</t>
+        </is>
+      </c>
+      <c r="P11" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="R11" s="70" t="inlineStr">
         <is>
           <t>XD B - 1</t>
         </is>
       </c>
-      <c r="N11" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 1</t>
-        </is>
-      </c>
-      <c r="P11" s="56" t="inlineStr">
+      <c r="S11" s="67" t="inlineStr">
+        <is>
+          <t>XD A - 2</t>
+        </is>
+      </c>
+      <c r="V11" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="X11" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="Z11" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="AB11" s="70" t="inlineStr">
+        <is>
+          <t>XD B - 2</t>
+        </is>
+      </c>
+      <c r="AE11" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 3</t>
+        </is>
+      </c>
+      <c r="AF11" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 3</t>
+        </is>
+      </c>
+      <c r="AG11" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 2</t>
+        </is>
+      </c>
+      <c r="AI11" s="75" t="inlineStr">
         <is>
           <t>MD A - 1</t>
         </is>
       </c>
-      <c r="T11" s="44" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="V11" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 2</t>
-        </is>
-      </c>
-      <c r="W11" s="56" t="inlineStr">
+      <c r="AK11" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AM11" s="69" t="inlineStr">
+        <is>
+          <t>WD B - 3</t>
+        </is>
+      </c>
+      <c r="AO11" s="75" t="inlineStr">
         <is>
           <t>MD A - 2</t>
         </is>
       </c>
-      <c r="Z11" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="AB11" s="52" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="AG11" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 2</t>
-        </is>
-      </c>
-      <c r="AI11" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="AP11" s="56" t="inlineStr">
-        <is>
-          <t>MD A - 3</t>
-        </is>
-      </c>
-      <c r="AV11" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AX11" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
+      <c r="AR11" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AT11" s="81" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
+        </is>
+      </c>
+      <c r="AX11" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 3</t>
         </is>
       </c>
     </row>
@@ -22964,44 +26469,69 @@
       <c r="B12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="48" t="inlineStr">
+      <c r="D12" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="F12" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="H12" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="J12" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="P12" s="80" t="inlineStr">
         <is>
           <t>MD C - 1</t>
         </is>
       </c>
-      <c r="P12" s="56" t="inlineStr">
+      <c r="V12" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="X12" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="Z12" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="AI12" s="75" t="inlineStr">
         <is>
           <t>MD A - 1</t>
         </is>
       </c>
-      <c r="T12" s="44" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="Z12" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="AB12" s="52" t="inlineStr">
-        <is>
-          <t>XD C - 2</t>
-        </is>
-      </c>
-      <c r="AI12" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="AV12" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
-        </is>
-      </c>
-      <c r="AX12" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
+      <c r="AK12" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AO12" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="AR12" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AT12" s="81" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
         </is>
       </c>
     </row>
@@ -23009,34 +26539,69 @@
       <c r="B13" t="n">
         <v>10</v>
       </c>
-      <c r="N13" s="48" t="inlineStr">
+      <c r="D13" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 1</t>
+        </is>
+      </c>
+      <c r="F13" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 1</t>
+        </is>
+      </c>
+      <c r="H13" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="J13" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="P13" s="80" t="inlineStr">
         <is>
           <t>MD C - 1</t>
         </is>
       </c>
-      <c r="P13" s="56" t="inlineStr">
+      <c r="V13" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="X13" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="Z13" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="AI13" s="75" t="inlineStr">
         <is>
           <t>MD A - 1</t>
         </is>
       </c>
-      <c r="T13" s="44" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="Z13" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="AI13" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="AX13" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
+      <c r="AK13" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AO13" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="AR13" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AT13" s="81" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
         </is>
       </c>
     </row>
@@ -23044,34 +26609,69 @@
       <c r="B14" t="n">
         <v>11</v>
       </c>
-      <c r="N14" s="48" t="inlineStr">
+      <c r="D14" s="71" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="F14" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 1</t>
+        </is>
+      </c>
+      <c r="H14" s="69" t="inlineStr">
+        <is>
+          <t>WD B - 1</t>
+        </is>
+      </c>
+      <c r="J14" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="P14" s="80" t="inlineStr">
         <is>
           <t>MD C - 1</t>
         </is>
       </c>
-      <c r="P14" s="56" t="inlineStr">
+      <c r="V14" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="X14" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="Z14" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="AI14" s="75" t="inlineStr">
         <is>
           <t>MD A - 1</t>
         </is>
       </c>
-      <c r="T14" s="44" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="Z14" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 1</t>
-        </is>
-      </c>
-      <c r="AI14" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 2</t>
-        </is>
-      </c>
-      <c r="AX14" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 1</t>
+      <c r="AK14" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AO14" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="AR14" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
+        </is>
+      </c>
+      <c r="AT14" s="81" t="inlineStr">
+        <is>
+          <t>WD A - 1</t>
         </is>
       </c>
     </row>
@@ -23079,19 +26679,64 @@
       <c r="B15" t="n">
         <v>12</v>
       </c>
-      <c r="T15" s="44" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="Z15" s="46" t="inlineStr">
+      <c r="D15" s="71" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="F15" s="65" t="inlineStr">
         <is>
           <t>MS B - 1</t>
         </is>
       </c>
-      <c r="AI15" s="46" t="inlineStr">
+      <c r="H15" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="J15" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="P15" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="V15" s="65" t="inlineStr">
         <is>
           <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="X15" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="Z15" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="AI15" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 2</t>
+        </is>
+      </c>
+      <c r="AK15" s="82" t="inlineStr">
+        <is>
+          <t>WD C - 1</t>
+        </is>
+      </c>
+      <c r="AO15" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 3</t>
+        </is>
+      </c>
+      <c r="AR15" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
         </is>
       </c>
     </row>
@@ -23099,19 +26744,49 @@
       <c r="B16" t="n">
         <v>13</v>
       </c>
-      <c r="T16" s="44" t="inlineStr">
-        <is>
-          <t>XD B - 2</t>
-        </is>
-      </c>
-      <c r="Z16" s="46" t="inlineStr">
+      <c r="D16" s="71" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="F16" s="65" t="inlineStr">
         <is>
           <t>MS B - 1</t>
         </is>
       </c>
-      <c r="AI16" s="46" t="inlineStr">
+      <c r="H16" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="J16" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="P16" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="V16" s="65" t="inlineStr">
         <is>
           <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="X16" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="Z16" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 2</t>
+        </is>
+      </c>
+      <c r="AR16" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
         </is>
       </c>
     </row>
@@ -23119,14 +26794,44 @@
       <c r="B17" t="n">
         <v>14</v>
       </c>
-      <c r="Z17" s="46" t="inlineStr">
+      <c r="D17" s="71" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="F17" s="65" t="inlineStr">
         <is>
           <t>MS B - 1</t>
         </is>
       </c>
-      <c r="AI17" s="46" t="inlineStr">
+      <c r="H17" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="J17" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="P17" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="V17" s="65" t="inlineStr">
         <is>
           <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="X17" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 2</t>
+        </is>
+      </c>
+      <c r="AR17" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
         </is>
       </c>
     </row>
@@ -23134,14 +26839,39 @@
       <c r="B18" t="n">
         <v>15</v>
       </c>
-      <c r="Z18" s="46" t="inlineStr">
+      <c r="D18" s="71" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="F18" s="65" t="inlineStr">
         <is>
           <t>MS B - 1</t>
         </is>
       </c>
-      <c r="AI18" s="46" t="inlineStr">
+      <c r="H18" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="J18" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="P18" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 1</t>
+        </is>
+      </c>
+      <c r="V18" s="65" t="inlineStr">
         <is>
           <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="AR18" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
         </is>
       </c>
     </row>
@@ -23149,14 +26879,34 @@
       <c r="B19" t="n">
         <v>16</v>
       </c>
-      <c r="Z19" s="46" t="inlineStr">
+      <c r="D19" s="71" t="inlineStr">
+        <is>
+          <t>XD C - 1</t>
+        </is>
+      </c>
+      <c r="F19" s="65" t="inlineStr">
         <is>
           <t>MS B - 1</t>
         </is>
       </c>
-      <c r="AI19" s="46" t="inlineStr">
+      <c r="H19" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="J19" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 1</t>
+        </is>
+      </c>
+      <c r="V19" s="65" t="inlineStr">
         <is>
           <t>MS B - 2</t>
+        </is>
+      </c>
+      <c r="AR19" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 2</t>
         </is>
       </c>
     </row>
@@ -23574,229 +27324,164 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="AT25" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="AV25" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>20:45</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="E26" s="57" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="F26" s="62" t="inlineStr">
+      <c r="C26" s="72" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="D26" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="E26" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 5</t>
+        </is>
+      </c>
+      <c r="F26" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="G26" s="82" t="inlineStr">
+        <is>
+          <t>WD C - 2</t>
+        </is>
+      </c>
+      <c r="H26" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="I26" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 4</t>
+        </is>
+      </c>
+      <c r="J26" s="74" t="inlineStr">
         <is>
           <t>WS B - 2</t>
         </is>
       </c>
-      <c r="G26" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="H26" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="I26" s="51" t="inlineStr">
+      <c r="L26" s="78" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="N26" s="83" t="inlineStr">
+        <is>
+          <t>WS C - 1</t>
+        </is>
+      </c>
+      <c r="O26" s="72" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="P26" s="77" t="inlineStr">
+        <is>
+          <t>WD V - 3</t>
+        </is>
+      </c>
+      <c r="R26" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 4</t>
+        </is>
+      </c>
+      <c r="S26" s="79" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="T26" s="83" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="U26" s="70" t="inlineStr">
+        <is>
+          <t>XD B - 4</t>
+        </is>
+      </c>
+      <c r="V26" s="67" t="inlineStr">
+        <is>
+          <t>XD A - 4</t>
+        </is>
+      </c>
+      <c r="W26" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 4</t>
+        </is>
+      </c>
+      <c r="Y26" s="69" t="inlineStr">
+        <is>
+          <t>WD B - 5</t>
+        </is>
+      </c>
+      <c r="Z26" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 5</t>
+        </is>
+      </c>
+      <c r="AA26" s="78" t="inlineStr">
         <is>
           <t>WS V - 3</t>
         </is>
       </c>
-      <c r="K26" s="57" t="inlineStr">
-        <is>
-          <t>MD V - 4</t>
-        </is>
-      </c>
-      <c r="L26" s="56" t="inlineStr">
-        <is>
-          <t>MD A - 4</t>
-        </is>
-      </c>
-      <c r="M26" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="N26" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="O26" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 5</t>
-        </is>
-      </c>
-      <c r="P26" s="59" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="Q26" s="49" t="inlineStr">
-        <is>
-          <t>WS C - 3</t>
-        </is>
-      </c>
-      <c r="R26" s="62" t="inlineStr">
-        <is>
-          <t>WS B - 4</t>
-        </is>
-      </c>
-      <c r="S26" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 1</t>
-        </is>
-      </c>
-      <c r="T26" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 4</t>
-        </is>
-      </c>
-      <c r="V26" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="W26" s="46" t="inlineStr">
+      <c r="AB26" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 5</t>
+        </is>
+      </c>
+      <c r="AC26" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 5</t>
+        </is>
+      </c>
+      <c r="AD26" s="65" t="inlineStr">
         <is>
           <t>MS B - 6</t>
         </is>
       </c>
-      <c r="X26" s="51" t="inlineStr">
+      <c r="AE26" s="82" t="inlineStr">
+        <is>
+          <t>WD C - 3</t>
+        </is>
+      </c>
+      <c r="AF26" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 5</t>
+        </is>
+      </c>
+      <c r="AH26" s="70" t="inlineStr">
+        <is>
+          <t>XD B - 5</t>
+        </is>
+      </c>
+      <c r="AJ26" s="72" t="inlineStr">
+        <is>
+          <t>MS V - 4</t>
+        </is>
+      </c>
+      <c r="AK26" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 6</t>
+        </is>
+      </c>
+      <c r="AL26" s="81" t="inlineStr">
+        <is>
+          <t>WD A - 4</t>
+        </is>
+      </c>
+      <c r="AN26" s="78" t="inlineStr">
         <is>
           <t>WS V - 4</t>
-        </is>
-      </c>
-      <c r="Y26" s="58" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AA26" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AC26" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 5</t>
-        </is>
-      </c>
-      <c r="AD26" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="AE26" s="55" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="AF26" s="55" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="AG26" s="59" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="AI26" s="58" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="AJ26" s="56" t="inlineStr">
-        <is>
-          <t>MD A - 5</t>
-        </is>
-      </c>
-      <c r="AL26" s="55" t="inlineStr">
-        <is>
-          <t>WD B - 3</t>
-        </is>
-      </c>
-      <c r="AM26" s="60" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="AO26" s="58" t="inlineStr">
-        <is>
-          <t>WD A - 3</t>
-        </is>
-      </c>
-      <c r="AP26" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 5</t>
-        </is>
-      </c>
-      <c r="AR26" s="55" t="inlineStr">
-        <is>
-          <t>WD B - 4</t>
-        </is>
-      </c>
-      <c r="AS26" s="59" t="inlineStr">
-        <is>
-          <t>MS V - 4</t>
-        </is>
-      </c>
-      <c r="AU26" s="58" t="inlineStr">
-        <is>
-          <t>WD A - 4</t>
-        </is>
-      </c>
-      <c r="AV26" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 6</t>
-        </is>
-      </c>
-      <c r="AX26" s="55" t="inlineStr">
-        <is>
-          <t>WD B - 5</t>
-        </is>
-      </c>
-      <c r="AY26" s="60" t="inlineStr">
-        <is>
-          <t>WD V - 4</t>
         </is>
       </c>
     </row>
@@ -23804,174 +27489,124 @@
       <c r="B27" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="E27" s="57" t="inlineStr">
-        <is>
-          <t>MD V - 3</t>
-        </is>
-      </c>
-      <c r="F27" s="62" t="inlineStr">
+      <c r="C27" s="72" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="D27" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="E27" s="65" t="inlineStr">
+        <is>
+          <t>MS B - 5</t>
+        </is>
+      </c>
+      <c r="F27" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="G27" s="82" t="inlineStr">
+        <is>
+          <t>WD C - 2</t>
+        </is>
+      </c>
+      <c r="H27" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="I27" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 4</t>
+        </is>
+      </c>
+      <c r="J27" s="74" t="inlineStr">
         <is>
           <t>WS B - 2</t>
         </is>
       </c>
-      <c r="G27" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="H27" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="I27" s="51" t="inlineStr">
+      <c r="L27" s="78" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="N27" s="83" t="inlineStr">
+        <is>
+          <t>WS C - 1</t>
+        </is>
+      </c>
+      <c r="O27" s="72" t="inlineStr">
+        <is>
+          <t>MS V - 3</t>
+        </is>
+      </c>
+      <c r="P27" s="77" t="inlineStr">
+        <is>
+          <t>WD V - 3</t>
+        </is>
+      </c>
+      <c r="R27" s="73" t="inlineStr">
+        <is>
+          <t>WS A - 4</t>
+        </is>
+      </c>
+      <c r="S27" s="79" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="T27" s="83" t="inlineStr">
+        <is>
+          <t>WS C - 2</t>
+        </is>
+      </c>
+      <c r="U27" s="70" t="inlineStr">
+        <is>
+          <t>XD B - 4</t>
+        </is>
+      </c>
+      <c r="W27" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 4</t>
+        </is>
+      </c>
+      <c r="Z27" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 5</t>
+        </is>
+      </c>
+      <c r="AA27" s="78" t="inlineStr">
         <is>
           <t>WS V - 3</t>
         </is>
       </c>
-      <c r="K27" s="49" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-      <c r="L27" s="56" t="inlineStr">
-        <is>
-          <t>MD A - 4</t>
-        </is>
-      </c>
-      <c r="M27" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="N27" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="O27" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 5</t>
-        </is>
-      </c>
-      <c r="P27" s="59" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="T27" s="53" t="inlineStr">
-        <is>
-          <t>XD V - 4</t>
-        </is>
-      </c>
-      <c r="V27" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="W27" s="55" t="inlineStr">
-        <is>
-          <t>WD B - 1</t>
-        </is>
-      </c>
-      <c r="X27" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="Y27" s="58" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AA27" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AC27" s="45" t="inlineStr">
-        <is>
-          <t>XD A - 4</t>
-        </is>
-      </c>
-      <c r="AD27" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="AE27" s="55" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="AF27" s="55" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="AG27" s="59" t="inlineStr">
-        <is>
-          <t>MS V - 3</t>
-        </is>
-      </c>
-      <c r="AI27" s="58" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="AJ27" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="AL27" s="55" t="inlineStr">
-        <is>
-          <t>WD B - 3</t>
-        </is>
-      </c>
-      <c r="AM27" s="60" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="AO27" s="58" t="inlineStr">
-        <is>
-          <t>WD A - 3</t>
-        </is>
-      </c>
-      <c r="AP27" s="47" t="inlineStr">
+      <c r="AC27" s="64" t="inlineStr">
         <is>
           <t>MS A - 5</t>
         </is>
       </c>
-      <c r="AR27" s="55" t="inlineStr">
-        <is>
-          <t>WD B - 4</t>
-        </is>
-      </c>
-      <c r="AS27" s="60" t="inlineStr">
-        <is>
-          <t>WD V - 3</t>
-        </is>
-      </c>
-      <c r="AU27" s="63" t="inlineStr">
+      <c r="AE27" s="82" t="inlineStr">
+        <is>
+          <t>WD C - 3</t>
+        </is>
+      </c>
+      <c r="AJ27" s="77" t="inlineStr">
+        <is>
+          <t>WD V - 4</t>
+        </is>
+      </c>
+      <c r="AK27" s="82" t="inlineStr">
         <is>
           <t>WD C - 4</t>
         </is>
       </c>
-      <c r="AV27" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 6</t>
-        </is>
-      </c>
-      <c r="AY27" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 6</t>
+      <c r="AN27" s="79" t="inlineStr">
+        <is>
+          <t>MD V - 4</t>
         </is>
       </c>
     </row>
@@ -23979,149 +27614,99 @@
       <c r="B28" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="E28" s="49" t="inlineStr">
+      <c r="C28" s="72" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="D28" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="E28" s="69" t="inlineStr">
+        <is>
+          <t>WD B - 4</t>
+        </is>
+      </c>
+      <c r="F28" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="G28" s="82" t="inlineStr">
+        <is>
+          <t>WD C - 2</t>
+        </is>
+      </c>
+      <c r="H28" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="I28" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 4</t>
+        </is>
+      </c>
+      <c r="J28" s="74" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="L28" s="78" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="N28" s="83" t="inlineStr">
         <is>
           <t>WS C - 1</t>
         </is>
       </c>
-      <c r="F28" s="62" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="G28" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="H28" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="I28" s="54" t="inlineStr">
-        <is>
-          <t>WS A - 5</t>
-        </is>
-      </c>
-      <c r="K28" s="49" t="inlineStr">
-        <is>
-          <t>WS C - 2</t>
-        </is>
-      </c>
-      <c r="L28" s="62" t="inlineStr">
+      <c r="O28" s="70" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="R28" s="75" t="inlineStr">
+        <is>
+          <t>MD A - 5</t>
+        </is>
+      </c>
+      <c r="S28" s="79" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="W28" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 4</t>
+        </is>
+      </c>
+      <c r="Z28" s="83" t="inlineStr">
+        <is>
+          <t>WS C - 3</t>
+        </is>
+      </c>
+      <c r="AA28" s="79" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="AC28" s="74" t="inlineStr">
         <is>
           <t>WS B - 3</t>
         </is>
       </c>
-      <c r="M28" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="N28" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="O28" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="P28" s="59" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="T28" s="45" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="V28" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="X28" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="Y28" s="58" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AA28" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AC28" s="63" t="inlineStr">
-        <is>
-          <t>WD C - 1</t>
-        </is>
-      </c>
-      <c r="AD28" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="AE28" s="55" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="AF28" s="55" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="AG28" s="60" t="inlineStr">
-        <is>
-          <t>WD V - 1</t>
-        </is>
-      </c>
-      <c r="AI28" s="58" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="AJ28" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="AL28" s="55" t="inlineStr">
-        <is>
-          <t>WD B - 3</t>
-        </is>
-      </c>
-      <c r="AM28" s="60" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="AO28" s="63" t="inlineStr">
-        <is>
-          <t>WD C - 3</t>
-        </is>
-      </c>
-      <c r="AP28" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 5</t>
-        </is>
-      </c>
-      <c r="AS28" s="60" t="inlineStr">
-        <is>
-          <t>WD V - 3</t>
+      <c r="AJ28" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 5</t>
+        </is>
+      </c>
+      <c r="AN28" s="74" t="inlineStr">
+        <is>
+          <t>WS B - 4</t>
         </is>
       </c>
     </row>
@@ -24129,134 +27714,89 @@
       <c r="B29" t="n">
         <v>4</v>
       </c>
-      <c r="C29" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="E29" s="49" t="inlineStr">
+      <c r="C29" s="72" t="inlineStr">
+        <is>
+          <t>MS V - 2</t>
+        </is>
+      </c>
+      <c r="D29" s="64" t="inlineStr">
+        <is>
+          <t>MS A - 4</t>
+        </is>
+      </c>
+      <c r="E29" s="69" t="inlineStr">
+        <is>
+          <t>WD B - 4</t>
+        </is>
+      </c>
+      <c r="F29" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 3</t>
+        </is>
+      </c>
+      <c r="G29" s="82" t="inlineStr">
+        <is>
+          <t>WD C - 2</t>
+        </is>
+      </c>
+      <c r="H29" s="66" t="inlineStr">
+        <is>
+          <t>XD V - 3</t>
+        </is>
+      </c>
+      <c r="I29" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 4</t>
+        </is>
+      </c>
+      <c r="J29" s="74" t="inlineStr">
+        <is>
+          <t>WS B - 2</t>
+        </is>
+      </c>
+      <c r="L29" s="78" t="inlineStr">
+        <is>
+          <t>WS V - 2</t>
+        </is>
+      </c>
+      <c r="N29" s="83" t="inlineStr">
         <is>
           <t>WS C - 1</t>
         </is>
       </c>
-      <c r="F29" s="62" t="inlineStr">
-        <is>
-          <t>WS B - 2</t>
-        </is>
-      </c>
-      <c r="G29" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="H29" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="I29" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="L29" s="62" t="inlineStr">
+      <c r="O29" s="70" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="R29" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 5</t>
+        </is>
+      </c>
+      <c r="S29" s="79" t="inlineStr">
+        <is>
+          <t>MD V - 2</t>
+        </is>
+      </c>
+      <c r="W29" s="80" t="inlineStr">
+        <is>
+          <t>MD C - 4</t>
+        </is>
+      </c>
+      <c r="AA29" s="79" t="inlineStr">
+        <is>
+          <t>MD V - 3</t>
+        </is>
+      </c>
+      <c r="AC29" s="74" t="inlineStr">
         <is>
           <t>WS B - 3</t>
         </is>
       </c>
-      <c r="M29" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="N29" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="O29" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="P29" s="59" t="inlineStr">
-        <is>
-          <t>MS V - 2</t>
-        </is>
-      </c>
-      <c r="T29" s="45" t="inlineStr">
-        <is>
-          <t>XD A - 3</t>
-        </is>
-      </c>
-      <c r="V29" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="X29" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="Y29" s="58" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AA29" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AD29" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 3</t>
-        </is>
-      </c>
-      <c r="AE29" s="55" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="AG29" s="60" t="inlineStr">
-        <is>
-          <t>WD V - 1</t>
-        </is>
-      </c>
-      <c r="AI29" s="58" t="inlineStr">
-        <is>
-          <t>WD A - 2</t>
-        </is>
-      </c>
-      <c r="AJ29" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="AL29" s="55" t="inlineStr">
-        <is>
-          <t>WD B - 3</t>
-        </is>
-      </c>
-      <c r="AM29" s="60" t="inlineStr">
-        <is>
-          <t>WD V - 2</t>
-        </is>
-      </c>
-      <c r="AO29" s="63" t="inlineStr">
-        <is>
-          <t>WD C - 3</t>
-        </is>
-      </c>
-      <c r="AP29" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 5</t>
-        </is>
-      </c>
-      <c r="AS29" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 5</t>
+      <c r="AN29" s="68" t="inlineStr">
+        <is>
+          <t>MD B - 6</t>
         </is>
       </c>
     </row>
@@ -24264,104 +27804,39 @@
       <c r="B30" t="n">
         <v>5</v>
       </c>
-      <c r="C30" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="E30" s="49" t="inlineStr">
-        <is>
-          <t>WS C - 1</t>
-        </is>
-      </c>
-      <c r="F30" s="48" t="inlineStr">
-        <is>
-          <t>MD C - 5</t>
-        </is>
-      </c>
-      <c r="G30" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="H30" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="I30" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="M30" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="N30" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="P30" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="V30" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="X30" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 4</t>
-        </is>
-      </c>
-      <c r="Y30" s="58" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AA30" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AD30" s="61" t="inlineStr">
+      <c r="C30" s="81" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="F30" s="76" t="inlineStr">
         <is>
           <t>MS C - 3</t>
         </is>
       </c>
-      <c r="AE30" s="55" t="inlineStr">
-        <is>
-          <t>WD B - 2</t>
-        </is>
-      </c>
-      <c r="AG30" s="60" t="inlineStr">
-        <is>
-          <t>WD V - 1</t>
-        </is>
-      </c>
-      <c r="AI30" s="63" t="inlineStr">
-        <is>
-          <t>WD C - 2</t>
-        </is>
-      </c>
-      <c r="AJ30" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 4</t>
-        </is>
-      </c>
-      <c r="AM30" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 4</t>
-        </is>
-      </c>
-      <c r="AS30" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 5</t>
+      <c r="H30" s="67" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="L30" s="75" t="inlineStr">
+        <is>
+          <t>MD A - 4</t>
+        </is>
+      </c>
+      <c r="O30" s="70" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
+        </is>
+      </c>
+      <c r="R30" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 5</t>
+        </is>
+      </c>
+      <c r="AC30" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 6</t>
         </is>
       </c>
     </row>
@@ -24369,84 +27844,29 @@
       <c r="B31" t="n">
         <v>6</v>
       </c>
-      <c r="C31" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="E31" s="49" t="inlineStr">
-        <is>
-          <t>WS C - 1</t>
-        </is>
-      </c>
-      <c r="G31" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="H31" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="I31" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="M31" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="N31" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="P31" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="V31" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="X31" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="Y31" s="58" t="inlineStr">
-        <is>
-          <t>WD A - 1</t>
-        </is>
-      </c>
-      <c r="AA31" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AD31" s="61" t="inlineStr">
+      <c r="C31" s="81" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="F31" s="76" t="inlineStr">
         <is>
           <t>MS C - 3</t>
         </is>
       </c>
-      <c r="AG31" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="AI31" s="63" t="inlineStr">
-        <is>
-          <t>WD C - 2</t>
-        </is>
-      </c>
-      <c r="AM31" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 4</t>
+      <c r="H31" s="67" t="inlineStr">
+        <is>
+          <t>XD A - 3</t>
+        </is>
+      </c>
+      <c r="L31" s="75" t="inlineStr">
+        <is>
+          <t>MD A - 4</t>
+        </is>
+      </c>
+      <c r="O31" s="70" t="inlineStr">
+        <is>
+          <t>XD B - 3</t>
         </is>
       </c>
     </row>
@@ -24454,74 +27874,19 @@
       <c r="B32" t="n">
         <v>7</v>
       </c>
-      <c r="C32" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="G32" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="H32" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="I32" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 4</t>
-        </is>
-      </c>
-      <c r="M32" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="N32" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="P32" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="V32" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="X32" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="AA32" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AD32" s="61" t="inlineStr">
+      <c r="C32" s="81" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="F32" s="76" t="inlineStr">
         <is>
           <t>MS C - 3</t>
         </is>
       </c>
-      <c r="AG32" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="AI32" s="63" t="inlineStr">
-        <is>
-          <t>WD C - 2</t>
-        </is>
-      </c>
-      <c r="AM32" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 4</t>
+      <c r="L32" s="81" t="inlineStr">
+        <is>
+          <t>WD A - 3</t>
         </is>
       </c>
     </row>
@@ -24529,64 +27894,19 @@
       <c r="B33" t="n">
         <v>8</v>
       </c>
-      <c r="C33" s="46" t="inlineStr">
-        <is>
-          <t>MS B - 3</t>
-        </is>
-      </c>
-      <c r="G33" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="H33" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 2</t>
-        </is>
-      </c>
-      <c r="N33" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="P33" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="V33" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="X33" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="AA33" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AD33" s="61" t="inlineStr">
+      <c r="C33" s="81" t="inlineStr">
+        <is>
+          <t>WD A - 2</t>
+        </is>
+      </c>
+      <c r="F33" s="76" t="inlineStr">
         <is>
           <t>MS C - 3</t>
         </is>
       </c>
-      <c r="AG33" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
-      <c r="AI33" s="63" t="inlineStr">
-        <is>
-          <t>WD C - 2</t>
-        </is>
-      </c>
-      <c r="AM33" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 4</t>
+      <c r="L33" s="81" t="inlineStr">
+        <is>
+          <t>WD A - 3</t>
         </is>
       </c>
     </row>
@@ -24594,29 +27914,9 @@
       <c r="B34" t="n">
         <v>9</v>
       </c>
-      <c r="N34" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 1</t>
-        </is>
-      </c>
-      <c r="P34" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="V34" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="AA34" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AG34" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
+      <c r="L34" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
         </is>
       </c>
     </row>
@@ -24624,24 +27924,9 @@
       <c r="B35" t="n">
         <v>10</v>
       </c>
-      <c r="P35" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="V35" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="AA35" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AG35" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
+      <c r="L35" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
         </is>
       </c>
     </row>
@@ -24649,24 +27934,9 @@
       <c r="B36" t="n">
         <v>11</v>
       </c>
-      <c r="P36" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="V36" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="AA36" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AG36" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
+      <c r="L36" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
         </is>
       </c>
     </row>
@@ -24674,24 +27944,9 @@
       <c r="B37" t="n">
         <v>12</v>
       </c>
-      <c r="P37" s="47" t="inlineStr">
-        <is>
-          <t>MS A - 3</t>
-        </is>
-      </c>
-      <c r="V37" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="AA37" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AG37" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
+      <c r="L37" s="76" t="inlineStr">
+        <is>
+          <t>MS C - 4</t>
         </is>
       </c>
     </row>
@@ -24699,50 +27954,20 @@
       <c r="B38" t="n">
         <v>13</v>
       </c>
-      <c r="V38" s="61" t="inlineStr">
-        <is>
-          <t>MS C - 2</t>
-        </is>
-      </c>
-      <c r="AA38" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
-      <c r="AG38" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 3</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
         <v>14</v>
       </c>
-      <c r="AA39" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
         <v>15</v>
       </c>
-      <c r="AA40" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
         <v>16</v>
-      </c>
-      <c r="AA41" s="50" t="inlineStr">
-        <is>
-          <t>MD B - 2</t>
-        </is>
       </c>
     </row>
     <row r="42">
@@ -24918,30 +28143,6 @@
         <f>COUNTA(AS26:AT41)</f>
         <v/>
       </c>
-      <c r="AT42">
-        <f>COUNTA(AT26:AU41)</f>
-        <v/>
-      </c>
-      <c r="AU42">
-        <f>COUNTA(AU26:AV41)</f>
-        <v/>
-      </c>
-      <c r="AV42">
-        <f>COUNTA(AV26:AW41)</f>
-        <v/>
-      </c>
-      <c r="AW42">
-        <f>COUNTA(AW26:AX41)</f>
-        <v/>
-      </c>
-      <c r="AX42">
-        <f>COUNTA(AX26:AY41)</f>
-        <v/>
-      </c>
-      <c r="AY42">
-        <f>COUNTA(AY26:AZ41)</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
